--- a/salidas/04_reglas.xlsx
+++ b/salidas/04_reglas.xlsx
@@ -466,14 +466,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,29 +531,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>entrenamiento</t>
+          <t>ajuste</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.16</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -564,29 +564,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>validación (3 últimas sem.)</t>
+          <t>validación</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.25</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>2.333333333333333</v>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -597,29 +597,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>prueba</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0.1153846153846154</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0.1538461538461539</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>3.25</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -630,29 +630,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>entrenamiento</t>
+          <t>ajuste</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.06944444444444445</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.1282051282051282</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>14.4</v>
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -663,29 +663,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>validación (3 últimas sem.)</t>
+          <t>validación</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.75</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>3.666666666666667</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -696,29 +696,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>prueba</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1204819277108434</v>
+        <v>0.375</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.6</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.2083333333333333</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>10.375</v>
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -729,29 +729,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>entrenamiento</t>
+          <t>ajuste</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>1.2</v>
+        <v>0.25</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -762,29 +762,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>validación (3 últimas sem.)</t>
+          <t>validación</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
-        <v>7</v>
-      </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.333333333333333</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
@@ -795,29 +795,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>prueba</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0.2307692307692308</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0.2608695652173913</v>
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -1172,7 +1172,7 @@
         <v>46237</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>46244</v>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
